--- a/docs/Cheklist_PM.xlsx
+++ b/docs/Cheklist_PM.xlsx
@@ -1667,7 +1667,7 @@
   <dimension ref="A1:E111"/>
   <sheetFormatPr defaultColWidth="11.50390625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="57.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="67.83"/>
